--- a/artfynd/A 31884-2024 artfynd.xlsx
+++ b/artfynd/A 31884-2024 artfynd.xlsx
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119536719</v>
+        <v>119536296</v>
       </c>
       <c r="B5" t="n">
-        <v>78262</v>
+        <v>97928</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,25 +1025,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574406</v>
+        <v>574412</v>
       </c>
       <c r="R5" t="n">
-        <v>7173206</v>
+        <v>7173113</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,7 +1125,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119537023</v>
+        <v>119537758</v>
       </c>
       <c r="B6" t="n">
         <v>78526</v>
@@ -1161,17 +1161,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Hällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574415</v>
+        <v>574423</v>
       </c>
       <c r="R6" t="n">
-        <v>7173117</v>
+        <v>7173139</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1195,22 +1195,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>20:35</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>20:35</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,17 +1220,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119537758</v>
+        <v>119537763</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
+        <v>79567</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1249,25 +1239,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1277,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574423</v>
+        <v>574401</v>
       </c>
       <c r="R7" t="n">
-        <v>7173139</v>
+        <v>7173101</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1339,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119536614</v>
+        <v>119536299</v>
       </c>
       <c r="B8" t="n">
-        <v>90399</v>
+        <v>57326</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1355,34 +1345,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6020</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Oljetagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sistotrema raduloides</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574394</v>
+        <v>574414</v>
       </c>
       <c r="R8" t="n">
-        <v>7173205</v>
+        <v>7173128</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1414,7 +1409,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1424,7 +1419,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1435,21 +1430,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1466,10 +1446,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119537763</v>
+        <v>119537023</v>
       </c>
       <c r="B9" t="n">
-        <v>79567</v>
+        <v>78526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1478,41 +1458,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hällmyran, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574401</v>
+        <v>574415</v>
       </c>
       <c r="R9" t="n">
-        <v>7173101</v>
+        <v>7173117</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1536,12 +1516,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,17 +1551,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Isak Vahlström, Christer Johansson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119536299</v>
+        <v>119536719</v>
       </c>
       <c r="B10" t="n">
-        <v>57326</v>
+        <v>78262</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1584,39 +1574,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574414</v>
+        <v>574406</v>
       </c>
       <c r="R10" t="n">
-        <v>7173128</v>
+        <v>7173206</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1648,7 +1633,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1658,7 +1643,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1685,10 +1670,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119536296</v>
+        <v>119536614</v>
       </c>
       <c r="B11" t="n">
-        <v>97928</v>
+        <v>90399</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1697,25 +1682,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>6020</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Oljetagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Sistotrema raduloides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Donk</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1725,10 +1710,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574412</v>
+        <v>574394</v>
       </c>
       <c r="R11" t="n">
-        <v>7173113</v>
+        <v>7173205</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1760,7 +1745,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>20:36</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1770,7 +1755,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>20:36</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1781,6 +1766,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">

--- a/artfynd/A 31884-2024 artfynd.xlsx
+++ b/artfynd/A 31884-2024 artfynd.xlsx
@@ -911,7 +911,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119537759</v>
+        <v>119537758</v>
       </c>
       <c r="B4" t="n">
         <v>78526</v>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574364</v>
+        <v>574423</v>
       </c>
       <c r="R4" t="n">
-        <v>7173153</v>
+        <v>7173139</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119536296</v>
+        <v>119537023</v>
       </c>
       <c r="B5" t="n">
-        <v>97928</v>
+        <v>78526</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,25 +1025,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574412</v>
+        <v>574415</v>
       </c>
       <c r="R5" t="n">
-        <v>7173113</v>
+        <v>7173117</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20:36</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>20:36</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119537758</v>
+        <v>119536299</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>57326</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,37 +1141,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hällmyran, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574423</v>
+        <v>574414</v>
       </c>
       <c r="R6" t="n">
-        <v>7173139</v>
+        <v>7173128</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1195,12 +1200,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,17 +1235,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Isak Vahlström, Christer Johansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119537763</v>
+        <v>119536719</v>
       </c>
       <c r="B7" t="n">
-        <v>79567</v>
+        <v>78262</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1239,41 +1254,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hällmyran, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574401</v>
+        <v>574406</v>
       </c>
       <c r="R7" t="n">
-        <v>7173101</v>
+        <v>7173206</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1297,12 +1312,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,17 +1347,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Isak Vahlström, Christer Johansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119536299</v>
+        <v>119537759</v>
       </c>
       <c r="B8" t="n">
-        <v>57326</v>
+        <v>78526</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,42 +1370,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Hällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574414</v>
+        <v>574364</v>
       </c>
       <c r="R8" t="n">
-        <v>7173128</v>
+        <v>7173153</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1404,22 +1424,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>20:35</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>20:35</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,17 +1449,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119537023</v>
+        <v>119537763</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>79567</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1458,41 +1468,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Hällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574415</v>
+        <v>574401</v>
       </c>
       <c r="R9" t="n">
-        <v>7173117</v>
+        <v>7173101</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1516,22 +1526,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>20:35</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>20:35</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,17 +1551,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119536719</v>
+        <v>119536296</v>
       </c>
       <c r="B10" t="n">
-        <v>78262</v>
+        <v>97928</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1570,25 +1570,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574406</v>
+        <v>574412</v>
       </c>
       <c r="R10" t="n">
-        <v>7173206</v>
+        <v>7173113</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 31884-2024 artfynd.xlsx
+++ b/artfynd/A 31884-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1795,6 +1795,210 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>118753880</v>
+      </c>
+      <c r="B12" t="n">
+        <v>90779</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Vilhelmina, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>574429</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7173158</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Louise Karlsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Louise Karlsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>118753921</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78646</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Vilhelmina, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>574429</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7173158</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Louise Karlsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Louise Karlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31884-2024 artfynd.xlsx
+++ b/artfynd/A 31884-2024 artfynd.xlsx
@@ -1797,10 +1797,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118753880</v>
+        <v>118753921</v>
       </c>
       <c r="B12" t="n">
-        <v>90779</v>
+        <v>78647</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>230405</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118753921</v>
+        <v>118753880</v>
       </c>
       <c r="B13" t="n">
-        <v>78646</v>
+        <v>90789</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>230405</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>

--- a/artfynd/A 31884-2024 artfynd.xlsx
+++ b/artfynd/A 31884-2024 artfynd.xlsx
@@ -1797,10 +1797,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118753921</v>
+        <v>118753880</v>
       </c>
       <c r="B12" t="n">
-        <v>78647</v>
+        <v>90801</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>230405</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118753880</v>
+        <v>118753921</v>
       </c>
       <c r="B13" t="n">
-        <v>90789</v>
+        <v>78652</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>230405</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>

--- a/artfynd/A 31884-2024 artfynd.xlsx
+++ b/artfynd/A 31884-2024 artfynd.xlsx
@@ -1797,10 +1797,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118753880</v>
+        <v>118753921</v>
       </c>
       <c r="B12" t="n">
-        <v>90801</v>
+        <v>78652</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>230405</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118753921</v>
+        <v>118753880</v>
       </c>
       <c r="B13" t="n">
-        <v>78652</v>
+        <v>90808</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>230405</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>

--- a/artfynd/A 31884-2024 artfynd.xlsx
+++ b/artfynd/A 31884-2024 artfynd.xlsx
@@ -1797,10 +1797,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118753921</v>
+        <v>118753880</v>
       </c>
       <c r="B12" t="n">
-        <v>78652</v>
+        <v>90813</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1813,21 +1813,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>230405</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
-        </is>
+        <v>1202</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1899,10 +1894,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118753880</v>
+        <v>118753921</v>
       </c>
       <c r="B13" t="n">
-        <v>90808</v>
+        <v>78653</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1915,21 +1910,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>230405</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>

--- a/artfynd/A 31884-2024 artfynd.xlsx
+++ b/artfynd/A 31884-2024 artfynd.xlsx
@@ -1797,10 +1797,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118753880</v>
+        <v>118753921</v>
       </c>
       <c r="B12" t="n">
-        <v>90813</v>
+        <v>78657</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1813,16 +1813,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>230405</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1894,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118753921</v>
+        <v>118753880</v>
       </c>
       <c r="B13" t="n">
-        <v>78653</v>
+        <v>90826</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1910,16 +1915,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>230405</v>
+        <v>1202</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>

--- a/artfynd/A 31884-2024 artfynd.xlsx
+++ b/artfynd/A 31884-2024 artfynd.xlsx
@@ -1797,10 +1797,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118753921</v>
+        <v>118753880</v>
       </c>
       <c r="B12" t="n">
-        <v>78657</v>
+        <v>90839</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>230405</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118753880</v>
+        <v>118753921</v>
       </c>
       <c r="B13" t="n">
-        <v>90826</v>
+        <v>78657</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>230405</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>

--- a/artfynd/A 31884-2024 artfynd.xlsx
+++ b/artfynd/A 31884-2024 artfynd.xlsx
@@ -1797,10 +1797,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118753880</v>
+        <v>118753921</v>
       </c>
       <c r="B12" t="n">
-        <v>90839</v>
+        <v>78657</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>230405</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118753921</v>
+        <v>118753880</v>
       </c>
       <c r="B13" t="n">
-        <v>78657</v>
+        <v>90839</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>230405</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>

--- a/artfynd/A 31884-2024 artfynd.xlsx
+++ b/artfynd/A 31884-2024 artfynd.xlsx
@@ -1797,10 +1797,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118753921</v>
+        <v>118753880</v>
       </c>
       <c r="B12" t="n">
-        <v>78657</v>
+        <v>90833</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>230405</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118753880</v>
+        <v>118753921</v>
       </c>
       <c r="B13" t="n">
-        <v>90839</v>
+        <v>78657</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>230405</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>

--- a/artfynd/A 31884-2024 artfynd.xlsx
+++ b/artfynd/A 31884-2024 artfynd.xlsx
@@ -1800,7 +1800,7 @@
         <v>118753880</v>
       </c>
       <c r="B12" t="n">
-        <v>90833</v>
+        <v>90834</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>118753921</v>
       </c>
       <c r="B13" t="n">
-        <v>78657</v>
+        <v>78658</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 31884-2024 artfynd.xlsx
+++ b/artfynd/A 31884-2024 artfynd.xlsx
@@ -1797,10 +1797,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118753880</v>
+        <v>118753921</v>
       </c>
       <c r="B12" t="n">
-        <v>90834</v>
+        <v>78661</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>230405</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118753921</v>
+        <v>118753880</v>
       </c>
       <c r="B13" t="n">
-        <v>78658</v>
+        <v>90837</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>230405</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>

--- a/artfynd/A 31884-2024 artfynd.xlsx
+++ b/artfynd/A 31884-2024 artfynd.xlsx
@@ -1797,10 +1797,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118753921</v>
+        <v>118753880</v>
       </c>
       <c r="B12" t="n">
-        <v>78661</v>
+        <v>90837</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>230405</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118753880</v>
+        <v>118753921</v>
       </c>
       <c r="B13" t="n">
-        <v>90837</v>
+        <v>78661</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>230405</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>

--- a/artfynd/A 31884-2024 artfynd.xlsx
+++ b/artfynd/A 31884-2024 artfynd.xlsx
@@ -1762,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG11" t="b">
         <v>0</v>

--- a/artfynd/A 31884-2024 artfynd.xlsx
+++ b/artfynd/A 31884-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1565368</v>
+        <v>118753880</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574423.7918533166</v>
+        <v>574429</v>
       </c>
       <c r="R2" t="n">
-        <v>7173168.256900158</v>
+        <v>7173158</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-07-26</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-07-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,36 +756,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>SCA Naturvärdesinventeringar</t>
+          <t>Louise Karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via SCA Naturvärdesinventeringar</t>
+          <t>Louise Karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97709753</v>
+        <v>119536015</v>
       </c>
       <c r="B3" t="n">
-        <v>57193</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,41 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>206004</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vilhelmina, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574341.7193274969</v>
+        <v>574453</v>
       </c>
       <c r="R3" t="n">
-        <v>7173174.377664863</v>
+        <v>7173174</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,22 +837,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-12-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-12-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,49 +867,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Isak Vahlström, Christer Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119537758</v>
+        <v>119537765</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -951,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574423</v>
+        <v>574394</v>
       </c>
       <c r="R4" t="n">
-        <v>7173139</v>
+        <v>7173055</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1013,15 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119537023</v>
+        <v>119535961</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1029,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1053,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574415</v>
+        <v>574445</v>
       </c>
       <c r="R5" t="n">
-        <v>7173117</v>
+        <v>7173171</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1088,7 +1046,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1098,7 +1056,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119536299</v>
+        <v>119536614</v>
       </c>
       <c r="B6" t="n">
-        <v>57326</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91738</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1141,39 +1094,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6020</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Oljetagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sistotrema raduloides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Donk</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574414</v>
+        <v>574394</v>
       </c>
       <c r="R6" t="n">
-        <v>7173128</v>
+        <v>7173205</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1205,7 +1153,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1215,17 +1163,32 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1242,50 +1205,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119536719</v>
+        <v>97709971</v>
       </c>
       <c r="B7" t="n">
-        <v>78262</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574406</v>
+        <v>574374</v>
       </c>
       <c r="R7" t="n">
-        <v>7173206</v>
+        <v>7173126</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1312,22 +1271,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>19:45</t>
+          <t>2021-12-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>19:45</t>
+          <t>2021-12-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,31 +1291,26 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Anna-Sara Karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Anna-Sara Karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119537759</v>
+        <v>119537023</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1390,17 +1334,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hällmyran, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574364</v>
+        <v>574415</v>
       </c>
       <c r="R8" t="n">
-        <v>7173153</v>
+        <v>7173117</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1424,12 +1368,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,44 +1403,39 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>Isak Vahlström, Christer Johansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119537763</v>
+        <v>119537742</v>
       </c>
       <c r="B9" t="n">
-        <v>79567</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1496,10 +1445,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574401</v>
+        <v>574381</v>
       </c>
       <c r="R9" t="n">
-        <v>7173101</v>
+        <v>7173062</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1558,50 +1507,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119536296</v>
+        <v>119537757</v>
       </c>
       <c r="B10" t="n">
-        <v>97928</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574412</v>
+        <v>574347</v>
       </c>
       <c r="R10" t="n">
-        <v>7173113</v>
+        <v>7173225</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1628,22 +1572,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>20:36</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>20:36</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1663,60 +1597,55 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119536614</v>
+        <v>119537758</v>
       </c>
       <c r="B11" t="n">
-        <v>90399</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6020</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oljetagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sistotrema raduloides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Hällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574394</v>
+        <v>574423</v>
       </c>
       <c r="R11" t="n">
-        <v>7173205</v>
+        <v>7173139</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1740,47 +1669,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>19:38</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>19:38</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1790,60 +1694,55 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Christer Johansson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118753880</v>
+        <v>119537759</v>
       </c>
       <c r="B12" t="n">
-        <v>90837</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vilhelmina, Ås lm</t>
+          <t>Hällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574429</v>
+        <v>574364</v>
       </c>
       <c r="R12" t="n">
-        <v>7173158</v>
+        <v>7173153</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1887,27 +1786,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Louise Karlsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Louise Karlsson</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118753921</v>
+        <v>119536719</v>
       </c>
       <c r="B13" t="n">
-        <v>78661</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1915,37 +1809,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>230405</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vilhelmina, Ås lm</t>
+          <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574429</v>
+        <v>574406</v>
       </c>
       <c r="R13" t="n">
-        <v>7173158</v>
+        <v>7173206</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1969,12 +1863,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1989,15 +1893,1253 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>119537761</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hällmyran, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>574382</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7173106</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>97710181</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Vilhelmina, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>574384</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7173046</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2021-12-26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2021-12-26</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anna-Sara Karlsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anna-Sara Karlsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>97709717</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80460</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Vilhelmina, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>574347</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7173225</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2021-12-26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2021-12-26</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anna-Sara Karlsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anna-Sara Karlsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>119536299</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bräntkullarna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>574414</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7173128</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>20:35</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>20:35</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>119537756</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hällmyran, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>574384</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7173238</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>119536053</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bräntkullarna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>574455</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7173175</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>20:27</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>20:27</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>97709974</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Vilhelmina, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>574419</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7173111</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2021-12-26</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2021-12-26</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anna-Sara Karlsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anna-Sara Karlsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>97709753</v>
+      </c>
+      <c r="B21" t="n">
+        <v>56522</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Vilhelmina, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>574342</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7173174</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2021-12-26</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2021-12-26</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anna-Sara Karlsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anna-Sara Karlsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>119536296</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Bräntkullarna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>574412</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7173113</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>20:36</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>20:36</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>119537763</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hällmyran, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>574401</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7173101</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>118752989</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Vilhelmina, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>574381</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7173106</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
           <t>Louise Karlsson</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
+      <c r="AX24" t="inlineStr">
         <is>
           <t>Louise Karlsson</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>118753921</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Vilhelmina, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>574429</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7173158</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Louise Karlsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Louise Karlsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
